--- a/Suivi_taches_MADAPORC.xlsx
+++ b/Suivi_taches_MADAPORC.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="Récapitulatif" sheetId="1" state="visible" r:id="rId3"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1080" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1076" uniqueCount="432">
   <si>
     <t xml:space="preserve">MADAPORC — Suivi des tâches &amp; fonctions par membre</t>
   </si>
@@ -1217,7 +1217,7 @@
     <t xml:space="preserve">Tâches transversales — exigences jury &amp; corrections (responsable / toute l'équipe)</t>
   </si>
   <si>
-    <t xml:space="preserve">Source : Plan de projet (responsable transversal) · README.md · correction.md</t>
+    <t xml:space="preserve">Durée totale estimée : 13.0 h   ·   Heures faites : 1,5 h   ·   Heures de retard : 11,5 h</t>
   </si>
   <si>
     <t xml:space="preserve">Catégorie</t>
@@ -1251,9 +1251,6 @@
   </si>
   <si>
     <t xml:space="preserve">—</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exigence README</t>
   </si>
   <si>
     <t xml:space="preserve">Recherche</t>
@@ -1441,7 +1438,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1474,6 +1471,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF000000"/>
+        <bgColor rgb="FF003300"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD9E1F2"/>
         <bgColor rgb="FFEDEDED"/>
       </patternFill>
@@ -1482,6 +1485,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFEDEDED"/>
         <bgColor rgb="FFD9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFEDEDED"/>
       </patternFill>
     </fill>
   </fills>
@@ -1534,124 +1543,136 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="33">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2325,29 +2346,29 @@
       <c r="G4" s="21"/>
       <c r="H4" s="21"/>
     </row>
-    <row r="7" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="s">
+    <row r="7" s="31" customFormat="true" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="H7" s="22" t="s">
         <v>68</v>
       </c>
     </row>
@@ -2358,15 +2379,15 @@
       <c r="B8" s="11" t="s">
         <v>375</v>
       </c>
-      <c r="C8" s="23" t="s">
+      <c r="C8" s="25" t="s">
         <v>376</v>
       </c>
       <c r="D8" s="11"/>
-      <c r="E8" s="24"/>
+      <c r="E8" s="26"/>
       <c r="F8" s="12" t="n">
         <v>200</v>
       </c>
-      <c r="G8" s="25" t="s">
+      <c r="G8" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H8" s="11"/>
@@ -2378,19 +2399,19 @@
       <c r="B9" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C9" s="23" t="s">
+      <c r="C9" s="25" t="s">
         <v>148</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>377</v>
       </c>
-      <c r="E9" s="24" t="s">
+      <c r="E9" s="26" t="s">
         <v>378</v>
       </c>
       <c r="F9" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="G9" s="25" t="s">
+      <c r="G9" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H9" s="11"/>
@@ -2402,19 +2423,19 @@
       <c r="B10" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C10" s="23" t="s">
+      <c r="C10" s="25" t="s">
         <v>148</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>379</v>
       </c>
-      <c r="E10" s="24" t="s">
+      <c r="E10" s="26" t="s">
         <v>380</v>
       </c>
       <c r="F10" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="G10" s="25" t="s">
+      <c r="G10" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H10" s="11"/>
@@ -2426,19 +2447,19 @@
       <c r="B11" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C11" s="23" t="s">
+      <c r="C11" s="25" t="s">
         <v>151</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>381</v>
       </c>
-      <c r="E11" s="24" t="s">
+      <c r="E11" s="26" t="s">
         <v>382</v>
       </c>
       <c r="F11" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="G11" s="25" t="s">
+      <c r="G11" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H11" s="11"/>
@@ -2450,19 +2471,19 @@
       <c r="B12" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C12" s="23" t="s">
+      <c r="C12" s="25" t="s">
         <v>151</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>383</v>
       </c>
-      <c r="E12" s="24" t="s">
+      <c r="E12" s="26" t="s">
         <v>384</v>
       </c>
       <c r="F12" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="G12" s="25" t="s">
+      <c r="G12" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H12" s="11"/>
@@ -2474,19 +2495,19 @@
       <c r="B13" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C13" s="23" t="s">
+      <c r="C13" s="25" t="s">
         <v>108</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>385</v>
       </c>
-      <c r="E13" s="24" t="s">
+      <c r="E13" s="26" t="s">
         <v>147</v>
       </c>
       <c r="F13" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G13" s="25" t="s">
+      <c r="G13" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H13" s="11"/>
@@ -2498,19 +2519,19 @@
       <c r="B14" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C14" s="23" t="s">
+      <c r="C14" s="25" t="s">
         <v>104</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>386</v>
       </c>
-      <c r="E14" s="24" t="s">
+      <c r="E14" s="26" t="s">
         <v>387</v>
       </c>
       <c r="F14" s="12" t="n">
         <v>150</v>
       </c>
-      <c r="G14" s="25" t="s">
+      <c r="G14" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H14" s="11"/>
@@ -2522,19 +2543,19 @@
       <c r="B15" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C15" s="23" t="s">
+      <c r="C15" s="25" t="s">
         <v>81</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="E15" s="24" t="s">
+      <c r="E15" s="26" t="s">
         <v>388</v>
       </c>
       <c r="F15" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="G15" s="25" t="s">
+      <c r="G15" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H15" s="11"/>
@@ -2546,28 +2567,28 @@
       <c r="B16" s="11" t="s">
         <v>389</v>
       </c>
-      <c r="C16" s="23" t="s">
+      <c r="C16" s="25" t="s">
         <v>390</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>391</v>
       </c>
-      <c r="E16" s="24" t="s">
+      <c r="E16" s="26" t="s">
         <v>392</v>
       </c>
       <c r="F16" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="G16" s="25" t="s">
+      <c r="G16" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H16" s="11"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E17" s="26" t="s">
+      <c r="E17" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="F17" s="27" t="n">
+      <c r="F17" s="29" t="n">
         <f aca="false">SUM(F8:F16)</f>
         <v>495</v>
       </c>
@@ -2595,7 +2616,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:H1048576"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
@@ -2607,43 +2628,56 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="32" t="s">
         <v>393</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>394</v>
-      </c>
+      <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
     </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="21" t="s">
+        <v>394</v>
+      </c>
+      <c r="B3" s="21"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
+    </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="22" t="s">
         <v>395</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="22" t="s">
         <v>396</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="22" t="s">
         <v>397</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="22" t="s">
         <v>68</v>
+      </c>
+      <c r="G4" s="22" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2665,6 +2699,9 @@
       <c r="F5" s="11" t="s">
         <v>400</v>
       </c>
+      <c r="G5" s="12" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="n">
@@ -2685,6 +2722,9 @@
       <c r="F6" s="11" t="s">
         <v>400</v>
       </c>
+      <c r="G6" s="12" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="n">
@@ -2704,6 +2744,9 @@
       </c>
       <c r="F7" s="11" t="s">
         <v>400</v>
+      </c>
+      <c r="G7" s="12" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2719,11 +2762,12 @@
       <c r="D8" s="11" t="s">
         <v>405</v>
       </c>
-      <c r="E8" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>406</v>
+      <c r="E8" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="11"/>
+      <c r="G8" s="12" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2731,19 +2775,20 @@
         <v>5</v>
       </c>
       <c r="B9" s="11" t="s">
+        <v>406</v>
+      </c>
+      <c r="C9" s="11" t="s">
         <v>407</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="D9" s="11" t="s">
         <v>408</v>
       </c>
-      <c r="D9" s="11" t="s">
-        <v>409</v>
-      </c>
-      <c r="E9" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>406</v>
+      <c r="E9" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" s="11"/>
+      <c r="G9" s="12" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2751,19 +2796,20 @@
         <v>6</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C10" s="11" t="s">
+        <v>409</v>
+      </c>
+      <c r="D10" s="11" t="s">
         <v>410</v>
       </c>
-      <c r="D10" s="11" t="s">
-        <v>411</v>
-      </c>
-      <c r="E10" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>406</v>
+      <c r="E10" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" s="11"/>
+      <c r="G10" s="12" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2771,19 +2817,20 @@
         <v>7</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>411</v>
-      </c>
-      <c r="E11" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>406</v>
+        <v>410</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="F11" s="11"/>
+      <c r="G11" s="12" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2791,19 +2838,20 @@
         <v>8</v>
       </c>
       <c r="B12" s="11" t="s">
+        <v>412</v>
+      </c>
+      <c r="C12" s="11" t="s">
         <v>413</v>
       </c>
-      <c r="C12" s="11" t="s">
-        <v>414</v>
-      </c>
       <c r="D12" s="11" t="s">
-        <v>411</v>
-      </c>
-      <c r="E12" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>406</v>
+        <v>410</v>
+      </c>
+      <c r="E12" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" s="11"/>
+      <c r="G12" s="12" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2811,19 +2859,20 @@
         <v>9</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>411</v>
-      </c>
-      <c r="E13" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="F13" s="11" t="s">
-        <v>406</v>
+        <v>410</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="F13" s="11"/>
+      <c r="G13" s="12" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2831,19 +2880,22 @@
         <v>10</v>
       </c>
       <c r="B14" s="11" t="s">
+        <v>415</v>
+      </c>
+      <c r="C14" s="11" t="s">
         <v>416</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>417</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>352</v>
       </c>
-      <c r="E14" s="28" t="s">
-        <v>4</v>
+      <c r="E14" s="27" t="s">
+        <v>3</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>418</v>
+        <v>417</v>
+      </c>
+      <c r="G14" s="12" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2851,19 +2903,22 @@
         <v>11</v>
       </c>
       <c r="B15" s="11" t="s">
+        <v>418</v>
+      </c>
+      <c r="C15" s="11" t="s">
         <v>419</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="D15" s="11" t="s">
         <v>420</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>421</v>
       </c>
       <c r="E15" s="15" t="s">
         <v>5</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>422</v>
+        <v>421</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2871,19 +2926,22 @@
         <v>12</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C16" s="11" t="s">
+        <v>422</v>
+      </c>
+      <c r="D16" s="11" t="s">
         <v>423</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>424</v>
       </c>
       <c r="E16" s="15" t="s">
         <v>5</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>425</v>
+        <v>424</v>
+      </c>
+      <c r="G16" s="12" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2891,19 +2949,22 @@
         <v>13</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C17" s="11" t="s">
+        <v>425</v>
+      </c>
+      <c r="D17" s="11" t="s">
         <v>426</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>427</v>
       </c>
       <c r="E17" s="15" t="s">
         <v>5</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>428</v>
+        <v>427</v>
+      </c>
+      <c r="G17" s="12" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2911,25 +2972,46 @@
         <v>14</v>
       </c>
       <c r="B18" s="11" t="s">
+        <v>428</v>
+      </c>
+      <c r="C18" s="11" t="s">
         <v>429</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="D18" s="11" t="s">
         <v>430</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="E18" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="F18" s="11" t="s">
         <v>431</v>
       </c>
-      <c r="E18" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="F18" s="11" t="s">
-        <v>432</v>
-      </c>
-    </row>
+      <c r="G18" s="12" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F19" s="28" t="s">
+        <v>113</v>
+      </c>
+      <c r="G19" s="0" t="n">
+        <f aca="false">SUM(G5:G18)</f>
+        <v>780</v>
+      </c>
+    </row>
+    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A3:H3"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3007,29 +3089,29 @@
       <c r="G4" s="21"/>
       <c r="H4" s="21"/>
     </row>
-    <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
+    <row r="6" s="23" customFormat="true" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="22" t="s">
         <v>68</v>
       </c>
     </row>
@@ -3037,22 +3119,22 @@
       <c r="A7" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C7" s="23" t="s">
+      <c r="B7" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="25" t="s">
         <v>70</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="E7" s="24" t="s">
+      <c r="E7" s="26" t="s">
         <v>72</v>
       </c>
       <c r="F7" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="G7" s="25" t="s">
+      <c r="G7" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H7" s="11"/>
@@ -3061,22 +3143,22 @@
       <c r="A8" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" s="23" t="s">
+      <c r="B8" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="25" t="s">
         <v>70</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="E8" s="24" t="s">
+      <c r="E8" s="26" t="s">
         <v>74</v>
       </c>
       <c r="F8" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="G8" s="25" t="s">
+      <c r="G8" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H8" s="11"/>
@@ -3085,22 +3167,22 @@
       <c r="A9" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C9" s="23" t="s">
+      <c r="B9" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" s="25" t="s">
         <v>75</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="E9" s="24" t="s">
+      <c r="E9" s="26" t="s">
         <v>77</v>
       </c>
       <c r="F9" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="G9" s="25" t="s">
+      <c r="G9" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H9" s="11"/>
@@ -3109,22 +3191,22 @@
       <c r="A10" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C10" s="23" t="s">
+      <c r="B10" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C10" s="25" t="s">
         <v>78</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="E10" s="24" t="s">
+      <c r="E10" s="26" t="s">
         <v>80</v>
       </c>
       <c r="F10" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="G10" s="25" t="s">
+      <c r="G10" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H10" s="11"/>
@@ -3133,22 +3215,22 @@
       <c r="A11" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C11" s="23" t="s">
+      <c r="B11" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" s="25" t="s">
         <v>81</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="E11" s="24" t="s">
+      <c r="E11" s="26" t="s">
         <v>83</v>
       </c>
       <c r="F11" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="G11" s="25" t="s">
+      <c r="G11" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H11" s="11"/>
@@ -3157,22 +3239,22 @@
       <c r="A12" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C12" s="23" t="s">
+      <c r="B12" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" s="25" t="s">
         <v>81</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="E12" s="24" t="s">
+      <c r="E12" s="26" t="s">
         <v>85</v>
       </c>
       <c r="F12" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="G12" s="25" t="s">
+      <c r="G12" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H12" s="11"/>
@@ -3181,22 +3263,22 @@
       <c r="A13" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C13" s="23" t="s">
+      <c r="B13" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13" s="25" t="s">
         <v>86</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="E13" s="24" t="s">
+      <c r="E13" s="26" t="s">
         <v>88</v>
       </c>
       <c r="F13" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="G13" s="25" t="s">
+      <c r="G13" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H13" s="11"/>
@@ -3205,22 +3287,22 @@
       <c r="A14" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C14" s="23" t="s">
+      <c r="B14" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" s="25" t="s">
         <v>89</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="E14" s="24" t="s">
+      <c r="E14" s="26" t="s">
         <v>91</v>
       </c>
       <c r="F14" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="G14" s="25" t="s">
+      <c r="G14" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H14" s="11"/>
@@ -3229,22 +3311,22 @@
       <c r="A15" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C15" s="23" t="s">
+      <c r="B15" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" s="25" t="s">
         <v>89</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="E15" s="24" t="s">
+      <c r="E15" s="26" t="s">
         <v>93</v>
       </c>
       <c r="F15" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="G15" s="25" t="s">
+      <c r="G15" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H15" s="11"/>
@@ -3253,22 +3335,22 @@
       <c r="A16" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C16" s="23" t="s">
+      <c r="B16" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" s="25" t="s">
         <v>89</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="24" t="s">
+      <c r="E16" s="26" t="s">
         <v>95</v>
       </c>
       <c r="F16" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="G16" s="25" t="s">
+      <c r="G16" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H16" s="11"/>
@@ -3277,22 +3359,22 @@
       <c r="A17" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="B17" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C17" s="23" t="s">
+      <c r="B17" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C17" s="25" t="s">
         <v>89</v>
       </c>
       <c r="D17" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="E17" s="24" t="s">
+      <c r="E17" s="26" t="s">
         <v>97</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="G17" s="25" t="s">
+      <c r="G17" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H17" s="11"/>
@@ -3304,19 +3386,19 @@
       <c r="B18" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C18" s="23" t="s">
+      <c r="C18" s="25" t="s">
         <v>99</v>
       </c>
       <c r="D18" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="E18" s="24" t="s">
+      <c r="E18" s="26" t="s">
         <v>101</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G18" s="25" t="s">
+      <c r="G18" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H18" s="11"/>
@@ -3328,19 +3410,19 @@
       <c r="B19" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C19" s="23" t="s">
+      <c r="C19" s="25" t="s">
         <v>99</v>
       </c>
       <c r="D19" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="E19" s="24" t="s">
+      <c r="E19" s="26" t="s">
         <v>102</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G19" s="25" t="s">
+      <c r="G19" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H19" s="11"/>
@@ -3352,19 +3434,19 @@
       <c r="B20" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C20" s="23" t="s">
+      <c r="C20" s="25" t="s">
         <v>99</v>
       </c>
       <c r="D20" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="E20" s="24" t="s">
+      <c r="E20" s="26" t="s">
         <v>103</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G20" s="25" t="s">
+      <c r="G20" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H20" s="11"/>
@@ -3376,19 +3458,19 @@
       <c r="B21" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C21" s="23" t="s">
+      <c r="C21" s="25" t="s">
         <v>104</v>
       </c>
       <c r="D21" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="E21" s="24" t="s">
+      <c r="E21" s="26" t="s">
         <v>106</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G21" s="25" t="s">
+      <c r="G21" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H21" s="11"/>
@@ -3400,19 +3482,19 @@
       <c r="B22" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C22" s="23" t="s">
+      <c r="C22" s="25" t="s">
         <v>104</v>
       </c>
       <c r="D22" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="E22" s="24" t="s">
+      <c r="E22" s="26" t="s">
         <v>107</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G22" s="25" t="s">
+      <c r="G22" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H22" s="11"/>
@@ -3424,19 +3506,19 @@
       <c r="B23" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C23" s="23" t="s">
+      <c r="C23" s="25" t="s">
         <v>108</v>
       </c>
       <c r="D23" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="E23" s="24" t="s">
+      <c r="E23" s="26" t="s">
         <v>110</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="G23" s="25" t="s">
+      <c r="G23" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H23" s="11"/>
@@ -3448,28 +3530,28 @@
       <c r="B24" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C24" s="23" t="s">
+      <c r="C24" s="25" t="s">
         <v>89</v>
       </c>
       <c r="D24" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="E24" s="24" t="s">
+      <c r="E24" s="26" t="s">
         <v>112</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="G24" s="25" t="s">
+      <c r="G24" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H24" s="11"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E25" s="26" t="s">
+      <c r="E25" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="F25" s="27" t="n">
+      <c r="F25" s="29" t="n">
         <v>440</v>
       </c>
     </row>
@@ -3556,29 +3638,29 @@
       <c r="G4" s="21"/>
       <c r="H4" s="21"/>
     </row>
-    <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
+    <row r="6" s="23" customFormat="true" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="22" t="s">
         <v>68</v>
       </c>
     </row>
@@ -3586,22 +3668,22 @@
       <c r="A7" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C7" s="23" t="s">
+      <c r="B7" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="25" t="s">
         <v>99</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="E7" s="24" t="s">
+      <c r="E7" s="26" t="s">
         <v>117</v>
       </c>
       <c r="F7" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G7" s="25" t="s">
+      <c r="G7" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H7" s="11"/>
@@ -3610,22 +3692,22 @@
       <c r="A8" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" s="23" t="s">
+      <c r="B8" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="25" t="s">
         <v>99</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="E8" s="24" t="s">
+      <c r="E8" s="26" t="s">
         <v>118</v>
       </c>
       <c r="F8" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G8" s="25" t="s">
+      <c r="G8" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H8" s="11"/>
@@ -3634,22 +3716,22 @@
       <c r="A9" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C9" s="23" t="s">
+      <c r="B9" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" s="25" t="s">
         <v>99</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="E9" s="24" t="s">
+      <c r="E9" s="26" t="s">
         <v>119</v>
       </c>
       <c r="F9" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G9" s="25" t="s">
+      <c r="G9" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H9" s="11"/>
@@ -3658,22 +3740,22 @@
       <c r="A10" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C10" s="23" t="s">
+      <c r="B10" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C10" s="25" t="s">
         <v>99</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="E10" s="24" t="s">
+      <c r="E10" s="26" t="s">
         <v>121</v>
       </c>
       <c r="F10" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G10" s="25" t="s">
+      <c r="G10" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H10" s="11"/>
@@ -3682,22 +3764,22 @@
       <c r="A11" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C11" s="23" t="s">
+      <c r="B11" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" s="25" t="s">
         <v>99</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="E11" s="24" t="s">
+      <c r="E11" s="26" t="s">
         <v>122</v>
       </c>
       <c r="F11" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G11" s="25" t="s">
+      <c r="G11" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H11" s="11"/>
@@ -3706,22 +3788,22 @@
       <c r="A12" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C12" s="23" t="s">
+      <c r="B12" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" s="25" t="s">
         <v>99</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="E12" s="24" t="s">
+      <c r="E12" s="26" t="s">
         <v>123</v>
       </c>
       <c r="F12" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G12" s="25" t="s">
+      <c r="G12" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H12" s="11"/>
@@ -3730,22 +3812,22 @@
       <c r="A13" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C13" s="23" t="s">
+      <c r="B13" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13" s="25" t="s">
         <v>99</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="E13" s="24" t="s">
+      <c r="E13" s="26" t="s">
         <v>124</v>
       </c>
       <c r="F13" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G13" s="25" t="s">
+      <c r="G13" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H13" s="11"/>
@@ -3754,22 +3836,22 @@
       <c r="A14" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C14" s="23" t="s">
+      <c r="B14" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" s="25" t="s">
         <v>104</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="E14" s="24" t="s">
+      <c r="E14" s="26" t="s">
         <v>126</v>
       </c>
       <c r="F14" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G14" s="25" t="s">
+      <c r="G14" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H14" s="11"/>
@@ -3778,22 +3860,22 @@
       <c r="A15" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C15" s="23" t="s">
+      <c r="B15" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" s="25" t="s">
         <v>104</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="E15" s="24" t="s">
+      <c r="E15" s="26" t="s">
         <v>127</v>
       </c>
       <c r="F15" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G15" s="25" t="s">
+      <c r="G15" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H15" s="11"/>
@@ -3802,22 +3884,22 @@
       <c r="A16" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C16" s="23" t="s">
+      <c r="B16" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" s="25" t="s">
         <v>104</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="E16" s="24" t="s">
+      <c r="E16" s="26" t="s">
         <v>128</v>
       </c>
       <c r="F16" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G16" s="25" t="s">
+      <c r="G16" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H16" s="11"/>
@@ -3826,22 +3908,22 @@
       <c r="A17" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="B17" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C17" s="23" t="s">
+      <c r="B17" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C17" s="25" t="s">
         <v>104</v>
       </c>
       <c r="D17" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="E17" s="24" t="s">
+      <c r="E17" s="26" t="s">
         <v>130</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>180</v>
       </c>
-      <c r="G17" s="25" t="s">
+      <c r="G17" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H17" s="11"/>
@@ -3850,22 +3932,22 @@
       <c r="A18" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="B18" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C18" s="23" t="s">
+      <c r="B18" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" s="25" t="s">
         <v>108</v>
       </c>
       <c r="D18" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="E18" s="24" t="s">
+      <c r="E18" s="26" t="s">
         <v>132</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G18" s="25" t="s">
+      <c r="G18" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H18" s="11"/>
@@ -3874,22 +3956,22 @@
       <c r="A19" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="B19" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C19" s="23" t="s">
+      <c r="B19" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C19" s="25" t="s">
         <v>133</v>
       </c>
       <c r="D19" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="E19" s="24" t="s">
+      <c r="E19" s="26" t="s">
         <v>135</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="G19" s="25" t="s">
+      <c r="G19" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H19" s="11"/>
@@ -3898,22 +3980,22 @@
       <c r="A20" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="B20" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C20" s="23" t="s">
+      <c r="B20" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C20" s="25" t="s">
         <v>89</v>
       </c>
       <c r="D20" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="E20" s="24" t="s">
+      <c r="E20" s="26" t="s">
         <v>137</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="G20" s="25" t="s">
+      <c r="G20" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H20" s="11"/>
@@ -3925,19 +4007,19 @@
       <c r="B21" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C21" s="23" t="s">
+      <c r="C21" s="25" t="s">
         <v>99</v>
       </c>
       <c r="D21" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="E21" s="24" t="s">
+      <c r="E21" s="26" t="s">
         <v>139</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G21" s="25" t="s">
+      <c r="G21" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H21" s="11"/>
@@ -3949,19 +4031,19 @@
       <c r="B22" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C22" s="23" t="s">
+      <c r="C22" s="25" t="s">
         <v>99</v>
       </c>
       <c r="D22" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="E22" s="24" t="s">
+      <c r="E22" s="26" t="s">
         <v>140</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G22" s="25" t="s">
+      <c r="G22" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H22" s="11"/>
@@ -3973,19 +4055,19 @@
       <c r="B23" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C23" s="23" t="s">
+      <c r="C23" s="25" t="s">
         <v>99</v>
       </c>
       <c r="D23" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="E23" s="24" t="s">
+      <c r="E23" s="26" t="s">
         <v>141</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G23" s="25" t="s">
+      <c r="G23" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H23" s="11"/>
@@ -3997,19 +4079,19 @@
       <c r="B24" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C24" s="23" t="s">
+      <c r="C24" s="25" t="s">
         <v>99</v>
       </c>
       <c r="D24" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="E24" s="24" t="s">
+      <c r="E24" s="26" t="s">
         <v>142</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G24" s="25" t="s">
+      <c r="G24" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H24" s="11" t="s">
@@ -4023,19 +4105,19 @@
       <c r="B25" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C25" s="23" t="s">
+      <c r="C25" s="25" t="s">
         <v>104</v>
       </c>
       <c r="D25" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="E25" s="24" t="s">
+      <c r="E25" s="26" t="s">
         <v>145</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>150</v>
       </c>
-      <c r="G25" s="25" t="s">
+      <c r="G25" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H25" s="11"/>
@@ -4047,19 +4129,19 @@
       <c r="B26" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C26" s="23" t="s">
+      <c r="C26" s="25" t="s">
         <v>108</v>
       </c>
       <c r="D26" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="E26" s="24" t="s">
+      <c r="E26" s="26" t="s">
         <v>147</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G26" s="25" t="s">
+      <c r="G26" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H26" s="11"/>
@@ -4071,19 +4153,19 @@
       <c r="B27" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C27" s="23" t="s">
+      <c r="C27" s="25" t="s">
         <v>148</v>
       </c>
       <c r="D27" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="E27" s="24" t="s">
+      <c r="E27" s="26" t="s">
         <v>150</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="G27" s="25" t="s">
+      <c r="G27" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H27" s="11"/>
@@ -4095,19 +4177,19 @@
       <c r="B28" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C28" s="23" t="s">
+      <c r="C28" s="25" t="s">
         <v>151</v>
       </c>
       <c r="D28" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="E28" s="24" t="s">
+      <c r="E28" s="26" t="s">
         <v>153</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="G28" s="25" t="s">
+      <c r="G28" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H28" s="11"/>
@@ -4119,28 +4201,28 @@
       <c r="B29" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C29" s="23" t="s">
+      <c r="C29" s="25" t="s">
         <v>89</v>
       </c>
       <c r="D29" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="E29" s="24" t="s">
+      <c r="E29" s="26" t="s">
         <v>155</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="G29" s="25" t="s">
+      <c r="G29" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H29" s="11"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E30" s="26" t="s">
+      <c r="E30" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="F30" s="27" t="n">
+      <c r="F30" s="29" t="n">
         <v>995</v>
       </c>
     </row>
@@ -4227,29 +4309,29 @@
       <c r="G4" s="21"/>
       <c r="H4" s="21"/>
     </row>
-    <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
+    <row r="6" s="23" customFormat="true" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="22" t="s">
         <v>68</v>
       </c>
     </row>
@@ -4257,22 +4339,22 @@
       <c r="A7" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C7" s="23" t="s">
+      <c r="B7" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="25" t="s">
         <v>99</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="E7" s="24" t="s">
+      <c r="E7" s="26" t="s">
         <v>159</v>
       </c>
       <c r="F7" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G7" s="25" t="s">
+      <c r="G7" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H7" s="11"/>
@@ -4281,22 +4363,22 @@
       <c r="A8" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" s="23" t="s">
+      <c r="B8" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="25" t="s">
         <v>99</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="E8" s="24" t="s">
+      <c r="E8" s="26" t="s">
         <v>160</v>
       </c>
       <c r="F8" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G8" s="25" t="s">
+      <c r="G8" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H8" s="11"/>
@@ -4305,22 +4387,22 @@
       <c r="A9" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C9" s="23" t="s">
+      <c r="B9" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" s="25" t="s">
         <v>99</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="E9" s="24" t="s">
+      <c r="E9" s="26" t="s">
         <v>161</v>
       </c>
       <c r="F9" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G9" s="25" t="s">
+      <c r="G9" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H9" s="11"/>
@@ -4329,22 +4411,22 @@
       <c r="A10" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C10" s="23" t="s">
+      <c r="B10" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C10" s="25" t="s">
         <v>99</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="E10" s="24" t="s">
+      <c r="E10" s="26" t="s">
         <v>162</v>
       </c>
       <c r="F10" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G10" s="25" t="s">
+      <c r="G10" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H10" s="11"/>
@@ -4353,22 +4435,22 @@
       <c r="A11" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C11" s="23" t="s">
+      <c r="B11" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" s="25" t="s">
         <v>99</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="E11" s="24" t="s">
+      <c r="E11" s="26" t="s">
         <v>163</v>
       </c>
       <c r="F11" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G11" s="25" t="s">
+      <c r="G11" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H11" s="11"/>
@@ -4377,22 +4459,22 @@
       <c r="A12" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C12" s="23" t="s">
+      <c r="B12" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" s="25" t="s">
         <v>104</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="E12" s="24" t="s">
+      <c r="E12" s="26" t="s">
         <v>165</v>
       </c>
       <c r="F12" s="12" t="n">
         <v>240</v>
       </c>
-      <c r="G12" s="25" t="s">
+      <c r="G12" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H12" s="11"/>
@@ -4401,22 +4483,22 @@
       <c r="A13" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C13" s="23" t="s">
+      <c r="B13" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13" s="25" t="s">
         <v>108</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="E13" s="24" t="s">
+      <c r="E13" s="26" t="s">
         <v>167</v>
       </c>
       <c r="F13" s="12" t="n">
         <v>90</v>
       </c>
-      <c r="G13" s="25" t="s">
+      <c r="G13" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H13" s="11"/>
@@ -4425,22 +4507,22 @@
       <c r="A14" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C14" s="23" t="s">
+      <c r="B14" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" s="25" t="s">
         <v>133</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="E14" s="24" t="s">
+      <c r="E14" s="26" t="s">
         <v>169</v>
       </c>
       <c r="F14" s="12" t="n">
         <v>75</v>
       </c>
-      <c r="G14" s="25" t="s">
+      <c r="G14" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H14" s="11"/>
@@ -4449,22 +4531,22 @@
       <c r="A15" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C15" s="23" t="s">
+      <c r="B15" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" s="25" t="s">
         <v>89</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="E15" s="24" t="s">
+      <c r="E15" s="26" t="s">
         <v>171</v>
       </c>
       <c r="F15" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="G15" s="25" t="s">
+      <c r="G15" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H15" s="11"/>
@@ -4473,22 +4555,22 @@
       <c r="A16" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C16" s="23" t="s">
+      <c r="B16" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" s="25" t="s">
         <v>99</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="E16" s="24" t="s">
+      <c r="E16" s="26" t="s">
         <v>173</v>
       </c>
       <c r="F16" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G16" s="25" t="s">
+      <c r="G16" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H16" s="11"/>
@@ -4497,22 +4579,22 @@
       <c r="A17" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="B17" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C17" s="23" t="s">
+      <c r="B17" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C17" s="25" t="s">
         <v>99</v>
       </c>
       <c r="D17" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="E17" s="24" t="s">
+      <c r="E17" s="26" t="s">
         <v>174</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G17" s="25" t="s">
+      <c r="G17" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H17" s="11"/>
@@ -4521,22 +4603,22 @@
       <c r="A18" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="B18" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C18" s="23" t="s">
+      <c r="B18" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" s="25" t="s">
         <v>104</v>
       </c>
       <c r="D18" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="E18" s="24" t="s">
+      <c r="E18" s="26" t="s">
         <v>176</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>150</v>
       </c>
-      <c r="G18" s="25" t="s">
+      <c r="G18" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H18" s="11"/>
@@ -4545,22 +4627,22 @@
       <c r="A19" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="B19" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C19" s="23" t="s">
+      <c r="B19" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C19" s="25" t="s">
         <v>108</v>
       </c>
       <c r="D19" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="E19" s="24" t="s">
+      <c r="E19" s="26" t="s">
         <v>178</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="G19" s="25" t="s">
+      <c r="G19" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H19" s="11"/>
@@ -4569,22 +4651,22 @@
       <c r="A20" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="B20" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C20" s="23" t="s">
+      <c r="B20" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C20" s="25" t="s">
         <v>179</v>
       </c>
       <c r="D20" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="E20" s="24" t="s">
+      <c r="E20" s="26" t="s">
         <v>181</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="G20" s="25" t="s">
+      <c r="G20" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H20" s="11"/>
@@ -4596,19 +4678,19 @@
       <c r="B21" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C21" s="23" t="s">
+      <c r="C21" s="25" t="s">
         <v>99</v>
       </c>
       <c r="D21" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="E21" s="24" t="s">
+      <c r="E21" s="26" t="s">
         <v>183</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>180</v>
       </c>
-      <c r="G21" s="25" t="s">
+      <c r="G21" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H21" s="11" t="s">
@@ -4622,19 +4704,19 @@
       <c r="B22" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C22" s="23" t="s">
+      <c r="C22" s="25" t="s">
         <v>104</v>
       </c>
       <c r="D22" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="E22" s="24" t="s">
+      <c r="E22" s="26" t="s">
         <v>186</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>180</v>
       </c>
-      <c r="G22" s="25" t="s">
+      <c r="G22" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H22" s="11" t="s">
@@ -4648,19 +4730,19 @@
       <c r="B23" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C23" s="23" t="s">
+      <c r="C23" s="25" t="s">
         <v>108</v>
       </c>
       <c r="D23" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="E23" s="24" t="s">
+      <c r="E23" s="26" t="s">
         <v>188</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="G23" s="25" t="s">
+      <c r="G23" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H23" s="11" t="s">
@@ -4674,19 +4756,19 @@
       <c r="B24" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C24" s="23" t="s">
+      <c r="C24" s="25" t="s">
         <v>148</v>
       </c>
       <c r="D24" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="E24" s="24" t="s">
+      <c r="E24" s="26" t="s">
         <v>191</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G24" s="25" t="s">
+      <c r="G24" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H24" s="11" t="s">
@@ -4700,19 +4782,19 @@
       <c r="B25" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C25" s="23" t="s">
+      <c r="C25" s="25" t="s">
         <v>151</v>
       </c>
       <c r="D25" s="11" t="s">
         <v>193</v>
       </c>
-      <c r="E25" s="24" t="s">
+      <c r="E25" s="26" t="s">
         <v>194</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="G25" s="25" t="s">
+      <c r="G25" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H25" s="11" t="s">
@@ -4726,28 +4808,28 @@
       <c r="B26" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C26" s="23" t="s">
+      <c r="C26" s="25" t="s">
         <v>89</v>
       </c>
       <c r="D26" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="E26" s="24" t="s">
+      <c r="E26" s="26" t="s">
         <v>197</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="G26" s="25" t="s">
+      <c r="G26" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H26" s="11"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E27" s="26" t="s">
+      <c r="E27" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="F27" s="27" t="n">
+      <c r="F27" s="29" t="n">
         <v>1400</v>
       </c>
     </row>
@@ -4834,29 +4916,29 @@
       <c r="G4" s="21"/>
       <c r="H4" s="21"/>
     </row>
-    <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
+    <row r="6" s="23" customFormat="true" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="22" t="s">
         <v>68</v>
       </c>
     </row>
@@ -4864,22 +4946,22 @@
       <c r="A7" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C7" s="23" t="s">
+      <c r="B7" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="25" t="s">
         <v>99</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="E7" s="24" t="s">
+      <c r="E7" s="26" t="s">
         <v>201</v>
       </c>
       <c r="F7" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G7" s="25" t="s">
+      <c r="G7" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H7" s="11"/>
@@ -4888,22 +4970,22 @@
       <c r="A8" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" s="23" t="s">
+      <c r="B8" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="25" t="s">
         <v>99</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="E8" s="24" t="s">
+      <c r="E8" s="26" t="s">
         <v>202</v>
       </c>
       <c r="F8" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G8" s="25" t="s">
+      <c r="G8" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H8" s="11"/>
@@ -4912,22 +4994,22 @@
       <c r="A9" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C9" s="23" t="s">
+      <c r="B9" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" s="25" t="s">
         <v>104</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="E9" s="24" t="s">
+      <c r="E9" s="26" t="s">
         <v>204</v>
       </c>
       <c r="F9" s="12" t="n">
         <v>90</v>
       </c>
-      <c r="G9" s="25" t="s">
+      <c r="G9" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H9" s="11"/>
@@ -4936,22 +5018,22 @@
       <c r="A10" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C10" s="23" t="s">
+      <c r="B10" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C10" s="25" t="s">
         <v>108</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>205</v>
       </c>
-      <c r="E10" s="24" t="s">
+      <c r="E10" s="26" t="s">
         <v>206</v>
       </c>
       <c r="F10" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="G10" s="25" t="s">
+      <c r="G10" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H10" s="11"/>
@@ -4960,22 +5042,22 @@
       <c r="A11" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C11" s="23" t="s">
+      <c r="B11" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" s="25" t="s">
         <v>179</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>207</v>
       </c>
-      <c r="E11" s="24" t="s">
+      <c r="E11" s="26" t="s">
         <v>208</v>
       </c>
       <c r="F11" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="G11" s="25" t="s">
+      <c r="G11" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H11" s="11"/>
@@ -4984,22 +5066,22 @@
       <c r="A12" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C12" s="23" t="s">
+      <c r="B12" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" s="25" t="s">
         <v>99</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="E12" s="24" t="s">
+      <c r="E12" s="26" t="s">
         <v>210</v>
       </c>
       <c r="F12" s="12" t="n">
         <v>90</v>
       </c>
-      <c r="G12" s="25" t="s">
+      <c r="G12" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H12" s="11"/>
@@ -5008,22 +5090,22 @@
       <c r="A13" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C13" s="23" t="s">
+      <c r="B13" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13" s="25" t="s">
         <v>99</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="E13" s="24" t="s">
+      <c r="E13" s="26" t="s">
         <v>212</v>
       </c>
       <c r="F13" s="12" t="n">
         <v>90</v>
       </c>
-      <c r="G13" s="25" t="s">
+      <c r="G13" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H13" s="11"/>
@@ -5032,22 +5114,22 @@
       <c r="A14" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C14" s="23" t="s">
+      <c r="B14" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" s="25" t="s">
         <v>99</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="E14" s="24" t="s">
+      <c r="E14" s="26" t="s">
         <v>214</v>
       </c>
       <c r="F14" s="12" t="n">
         <v>90</v>
       </c>
-      <c r="G14" s="25" t="s">
+      <c r="G14" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H14" s="11"/>
@@ -5056,22 +5138,22 @@
       <c r="A15" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C15" s="23" t="s">
+      <c r="B15" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" s="25" t="s">
         <v>104</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="E15" s="24" t="s">
+      <c r="E15" s="26" t="s">
         <v>216</v>
       </c>
       <c r="F15" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G15" s="25" t="s">
+      <c r="G15" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H15" s="11"/>
@@ -5080,22 +5162,22 @@
       <c r="A16" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C16" s="23" t="s">
+      <c r="B16" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" s="25" t="s">
         <v>108</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="E16" s="24" t="s">
+      <c r="E16" s="26" t="s">
         <v>218</v>
       </c>
       <c r="F16" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="G16" s="25" t="s">
+      <c r="G16" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H16" s="11"/>
@@ -5104,22 +5186,22 @@
       <c r="A17" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="B17" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C17" s="23" t="s">
+      <c r="B17" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C17" s="25" t="s">
         <v>148</v>
       </c>
       <c r="D17" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="E17" s="24" t="s">
+      <c r="E17" s="26" t="s">
         <v>220</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>75</v>
       </c>
-      <c r="G17" s="25" t="s">
+      <c r="G17" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H17" s="11"/>
@@ -5128,22 +5210,22 @@
       <c r="A18" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="B18" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C18" s="23" t="s">
+      <c r="B18" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" s="25" t="s">
         <v>151</v>
       </c>
       <c r="D18" s="11" t="s">
         <v>221</v>
       </c>
-      <c r="E18" s="24" t="s">
+      <c r="E18" s="26" t="s">
         <v>222</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G18" s="25" t="s">
+      <c r="G18" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H18" s="11"/>
@@ -5152,31 +5234,31 @@
       <c r="A19" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="B19" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C19" s="23" t="s">
+      <c r="B19" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C19" s="25" t="s">
         <v>89</v>
       </c>
       <c r="D19" s="11" t="s">
         <v>223</v>
       </c>
-      <c r="E19" s="24" t="s">
+      <c r="E19" s="26" t="s">
         <v>224</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>120</v>
       </c>
-      <c r="G19" s="25" t="s">
+      <c r="G19" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H19" s="11"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E20" s="26" t="s">
+      <c r="E20" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="F20" s="27" t="n">
+      <c r="F20" s="29" t="n">
         <v>750</v>
       </c>
     </row>
@@ -5263,29 +5345,29 @@
       <c r="G4" s="21"/>
       <c r="H4" s="21"/>
     </row>
-    <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
+    <row r="6" s="23" customFormat="true" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="22" t="s">
         <v>68</v>
       </c>
     </row>
@@ -5293,22 +5375,22 @@
       <c r="A7" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C7" s="23" t="s">
+      <c r="B7" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="25" t="s">
         <v>99</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="E7" s="24" t="s">
+      <c r="E7" s="26" t="s">
         <v>228</v>
       </c>
       <c r="F7" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G7" s="25" t="s">
+      <c r="G7" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H7" s="11"/>
@@ -5317,22 +5399,22 @@
       <c r="A8" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" s="23" t="s">
+      <c r="B8" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="25" t="s">
         <v>99</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="E8" s="24" t="s">
+      <c r="E8" s="26" t="s">
         <v>229</v>
       </c>
       <c r="F8" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G8" s="25" t="s">
+      <c r="G8" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H8" s="11"/>
@@ -5341,22 +5423,22 @@
       <c r="A9" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C9" s="23" t="s">
+      <c r="B9" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" s="25" t="s">
         <v>99</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="E9" s="24" t="s">
+      <c r="E9" s="26" t="s">
         <v>230</v>
       </c>
       <c r="F9" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G9" s="25" t="s">
+      <c r="G9" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H9" s="11"/>
@@ -5365,22 +5447,22 @@
       <c r="A10" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C10" s="23" t="s">
+      <c r="B10" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C10" s="25" t="s">
         <v>104</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>231</v>
       </c>
-      <c r="E10" s="24" t="s">
+      <c r="E10" s="26" t="s">
         <v>232</v>
       </c>
       <c r="F10" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G10" s="25" t="s">
+      <c r="G10" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H10" s="11"/>
@@ -5389,22 +5471,22 @@
       <c r="A11" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C11" s="23" t="s">
+      <c r="B11" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" s="25" t="s">
         <v>104</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>231</v>
       </c>
-      <c r="E11" s="24" t="s">
+      <c r="E11" s="26" t="s">
         <v>233</v>
       </c>
       <c r="F11" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G11" s="25" t="s">
+      <c r="G11" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H11" s="11"/>
@@ -5413,22 +5495,22 @@
       <c r="A12" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C12" s="23" t="s">
+      <c r="B12" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" s="25" t="s">
         <v>104</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>231</v>
       </c>
-      <c r="E12" s="24" t="s">
+      <c r="E12" s="26" t="s">
         <v>234</v>
       </c>
       <c r="F12" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G12" s="25" t="s">
+      <c r="G12" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H12" s="11"/>
@@ -5437,22 +5519,22 @@
       <c r="A13" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C13" s="23" t="s">
+      <c r="B13" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13" s="25" t="s">
         <v>104</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>231</v>
       </c>
-      <c r="E13" s="24" t="s">
+      <c r="E13" s="26" t="s">
         <v>235</v>
       </c>
       <c r="F13" s="12" t="n">
         <v>90</v>
       </c>
-      <c r="G13" s="25" t="s">
+      <c r="G13" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H13" s="11"/>
@@ -5461,22 +5543,22 @@
       <c r="A14" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C14" s="23" t="s">
+      <c r="B14" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" s="25" t="s">
         <v>104</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>231</v>
       </c>
-      <c r="E14" s="24" t="s">
+      <c r="E14" s="26" t="s">
         <v>236</v>
       </c>
       <c r="F14" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G14" s="25" t="s">
+      <c r="G14" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H14" s="11"/>
@@ -5485,22 +5567,22 @@
       <c r="A15" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C15" s="23" t="s">
+      <c r="B15" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" s="25" t="s">
         <v>104</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="E15" s="24" t="s">
+      <c r="E15" s="26" t="s">
         <v>238</v>
       </c>
       <c r="F15" s="12" t="n">
         <v>90</v>
       </c>
-      <c r="G15" s="25" t="s">
+      <c r="G15" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H15" s="11"/>
@@ -5509,22 +5591,22 @@
       <c r="A16" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C16" s="23" t="s">
+      <c r="B16" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" s="25" t="s">
         <v>108</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="E16" s="24" t="s">
+      <c r="E16" s="26" t="s">
         <v>240</v>
       </c>
       <c r="F16" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="G16" s="25" t="s">
+      <c r="G16" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H16" s="11"/>
@@ -5533,22 +5615,22 @@
       <c r="A17" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="B17" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C17" s="23" t="s">
+      <c r="B17" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C17" s="25" t="s">
         <v>108</v>
       </c>
       <c r="D17" s="11" t="s">
         <v>241</v>
       </c>
-      <c r="E17" s="24" t="s">
+      <c r="E17" s="26" t="s">
         <v>242</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="G17" s="25" t="s">
+      <c r="G17" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H17" s="11"/>
@@ -5557,22 +5639,22 @@
       <c r="A18" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="B18" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C18" s="23" t="s">
+      <c r="B18" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" s="25" t="s">
         <v>179</v>
       </c>
       <c r="D18" s="11" t="s">
         <v>243</v>
       </c>
-      <c r="E18" s="24" t="s">
+      <c r="E18" s="26" t="s">
         <v>244</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>90</v>
       </c>
-      <c r="G18" s="25" t="s">
+      <c r="G18" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H18" s="11"/>
@@ -5584,13 +5666,13 @@
       <c r="B19" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C19" s="23" t="s">
+      <c r="C19" s="25" t="s">
         <v>99</v>
       </c>
       <c r="D19" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="E19" s="24" t="s">
+      <c r="E19" s="26" t="s">
         <v>246</v>
       </c>
       <c r="F19" s="12" t="n">
@@ -5610,13 +5692,13 @@
       <c r="B20" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C20" s="23" t="s">
+      <c r="C20" s="25" t="s">
         <v>104</v>
       </c>
       <c r="D20" s="11" t="s">
         <v>247</v>
       </c>
-      <c r="E20" s="24" t="s">
+      <c r="E20" s="26" t="s">
         <v>248</v>
       </c>
       <c r="F20" s="12" t="n">
@@ -5636,19 +5718,19 @@
       <c r="B21" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C21" s="23" t="s">
+      <c r="C21" s="25" t="s">
         <v>108</v>
       </c>
       <c r="D21" s="11" t="s">
         <v>249</v>
       </c>
-      <c r="E21" s="24" t="s">
+      <c r="E21" s="26" t="s">
         <v>250</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="G21" s="25" t="s">
+      <c r="G21" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H21" s="11" t="s">
@@ -5662,19 +5744,19 @@
       <c r="B22" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C22" s="23" t="s">
+      <c r="C22" s="25" t="s">
         <v>148</v>
       </c>
       <c r="D22" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="E22" s="24" t="s">
+      <c r="E22" s="26" t="s">
         <v>253</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="G22" s="25" t="s">
+      <c r="G22" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H22" s="11" t="s">
@@ -5688,19 +5770,19 @@
       <c r="B23" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C23" s="23" t="s">
+      <c r="C23" s="25" t="s">
         <v>151</v>
       </c>
       <c r="D23" s="11" t="s">
         <v>254</v>
       </c>
-      <c r="E23" s="24" t="s">
+      <c r="E23" s="26" t="s">
         <v>255</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="G23" s="28" t="s">
+      <c r="G23" s="30" t="s">
         <v>4</v>
       </c>
       <c r="H23" s="11" t="s">
@@ -5714,28 +5796,28 @@
       <c r="B24" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C24" s="23" t="s">
+      <c r="C24" s="25" t="s">
         <v>89</v>
       </c>
       <c r="D24" s="11" t="s">
         <v>256</v>
       </c>
-      <c r="E24" s="24" t="s">
+      <c r="E24" s="26" t="s">
         <v>257</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="G24" s="25" t="s">
+      <c r="G24" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H24" s="11"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E25" s="26" t="s">
+      <c r="E25" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="F25" s="27" t="n">
+      <c r="F25" s="29" t="n">
         <v>990</v>
       </c>
     </row>
@@ -5822,29 +5904,29 @@
       <c r="G4" s="21"/>
       <c r="H4" s="21"/>
     </row>
-    <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
+    <row r="6" s="23" customFormat="true" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="22" t="s">
         <v>68</v>
       </c>
     </row>
@@ -5852,22 +5934,22 @@
       <c r="A7" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C7" s="23" t="s">
+      <c r="B7" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="25" t="s">
         <v>99</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="E7" s="24" t="s">
+      <c r="E7" s="26" t="s">
         <v>260</v>
       </c>
       <c r="F7" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G7" s="25" t="s">
+      <c r="G7" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H7" s="11"/>
@@ -5876,22 +5958,22 @@
       <c r="A8" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" s="23" t="s">
+      <c r="B8" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="25" t="s">
         <v>99</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="E8" s="24" t="s">
+      <c r="E8" s="26" t="s">
         <v>261</v>
       </c>
       <c r="F8" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G8" s="25" t="s">
+      <c r="G8" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H8" s="11" t="e">
@@ -5903,22 +5985,22 @@
       <c r="A9" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C9" s="23" t="s">
+      <c r="B9" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" s="25" t="s">
         <v>99</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="E9" s="24" t="s">
+      <c r="E9" s="26" t="s">
         <v>262</v>
       </c>
       <c r="F9" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G9" s="25" t="s">
+      <c r="G9" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H9" s="11"/>
@@ -5927,22 +6009,22 @@
       <c r="A10" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C10" s="23" t="s">
+      <c r="B10" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C10" s="25" t="s">
         <v>99</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="E10" s="24" t="s">
+      <c r="E10" s="26" t="s">
         <v>263</v>
       </c>
       <c r="F10" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G10" s="25" t="s">
+      <c r="G10" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H10" s="11" t="s">
@@ -5953,22 +6035,22 @@
       <c r="A11" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C11" s="23" t="s">
+      <c r="B11" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" s="25" t="s">
         <v>104</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="E11" s="24" t="s">
+      <c r="E11" s="26" t="s">
         <v>266</v>
       </c>
       <c r="F11" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G11" s="25" t="s">
+      <c r="G11" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H11" s="11"/>
@@ -5977,22 +6059,22 @@
       <c r="A12" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C12" s="23" t="s">
+      <c r="B12" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" s="25" t="s">
         <v>104</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="E12" s="24" t="s">
+      <c r="E12" s="26" t="s">
         <v>267</v>
       </c>
       <c r="F12" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G12" s="25" t="s">
+      <c r="G12" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H12" s="11"/>
@@ -6001,22 +6083,22 @@
       <c r="A13" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C13" s="23" t="s">
+      <c r="B13" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13" s="25" t="s">
         <v>104</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="E13" s="24" t="s">
+      <c r="E13" s="26" t="s">
         <v>268</v>
       </c>
       <c r="F13" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G13" s="25" t="s">
+      <c r="G13" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H13" s="11"/>
@@ -6025,22 +6107,22 @@
       <c r="A14" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C14" s="23" t="s">
+      <c r="B14" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" s="25" t="s">
         <v>104</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="E14" s="24" t="s">
+      <c r="E14" s="26" t="s">
         <v>269</v>
       </c>
       <c r="F14" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G14" s="25" t="s">
+      <c r="G14" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H14" s="11"/>
@@ -6049,22 +6131,22 @@
       <c r="A15" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C15" s="23" t="s">
+      <c r="B15" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" s="25" t="s">
         <v>104</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="E15" s="24" t="s">
+      <c r="E15" s="26" t="s">
         <v>270</v>
       </c>
       <c r="F15" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G15" s="25" t="s">
+      <c r="G15" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H15" s="11" t="s">
@@ -6075,22 +6157,22 @@
       <c r="A16" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C16" s="23" t="s">
+      <c r="B16" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" s="25" t="s">
         <v>104</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="E16" s="24" t="s">
+      <c r="E16" s="26" t="s">
         <v>272</v>
       </c>
       <c r="F16" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G16" s="25" t="s">
+      <c r="G16" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H16" s="11" t="s">
@@ -6101,22 +6183,22 @@
       <c r="A17" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="B17" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C17" s="23" t="s">
+      <c r="B17" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C17" s="25" t="s">
         <v>104</v>
       </c>
       <c r="D17" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="E17" s="24" t="s">
+      <c r="E17" s="26" t="s">
         <v>273</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G17" s="25" t="s">
+      <c r="G17" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H17" s="11" t="s">
@@ -6127,22 +6209,22 @@
       <c r="A18" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="B18" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C18" s="23" t="s">
+      <c r="B18" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" s="25" t="s">
         <v>104</v>
       </c>
       <c r="D18" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="E18" s="24" t="s">
+      <c r="E18" s="26" t="s">
         <v>275</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G18" s="25" t="s">
+      <c r="G18" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H18" s="11" t="s">
@@ -6153,22 +6235,22 @@
       <c r="A19" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="B19" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C19" s="23" t="s">
+      <c r="B19" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C19" s="25" t="s">
         <v>104</v>
       </c>
       <c r="D19" s="11" t="s">
         <v>276</v>
       </c>
-      <c r="E19" s="24" t="s">
+      <c r="E19" s="26" t="s">
         <v>277</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G19" s="25" t="s">
+      <c r="G19" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H19" s="11" t="s">
@@ -6179,22 +6261,22 @@
       <c r="A20" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="B20" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C20" s="23" t="s">
+      <c r="B20" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C20" s="25" t="s">
         <v>104</v>
       </c>
       <c r="D20" s="11" t="s">
         <v>276</v>
       </c>
-      <c r="E20" s="24" t="s">
+      <c r="E20" s="26" t="s">
         <v>279</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G20" s="25" t="s">
+      <c r="G20" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H20" s="11" t="s">
@@ -6205,22 +6287,22 @@
       <c r="A21" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="B21" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C21" s="23" t="s">
+      <c r="B21" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C21" s="25" t="s">
         <v>151</v>
       </c>
       <c r="D21" s="11" t="s">
         <v>280</v>
       </c>
-      <c r="E21" s="24" t="s">
+      <c r="E21" s="26" t="s">
         <v>281</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="G21" s="25" t="s">
+      <c r="G21" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H21" s="11"/>
@@ -6229,22 +6311,22 @@
       <c r="A22" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="B22" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C22" s="23" t="s">
+      <c r="B22" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C22" s="25" t="s">
         <v>89</v>
       </c>
       <c r="D22" s="11" t="s">
         <v>282</v>
       </c>
-      <c r="E22" s="24" t="s">
+      <c r="E22" s="26" t="s">
         <v>283</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="G22" s="25" t="s">
+      <c r="G22" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H22" s="11"/>
@@ -6256,19 +6338,19 @@
       <c r="B23" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C23" s="23" t="s">
+      <c r="C23" s="25" t="s">
         <v>99</v>
       </c>
       <c r="D23" s="11" t="s">
         <v>284</v>
       </c>
-      <c r="E23" s="24" t="s">
+      <c r="E23" s="26" t="s">
         <v>285</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G23" s="25" t="s">
+      <c r="G23" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H23" s="11" t="s">
@@ -6282,19 +6364,19 @@
       <c r="B24" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C24" s="23" t="s">
+      <c r="C24" s="25" t="s">
         <v>104</v>
       </c>
       <c r="D24" s="11" t="s">
         <v>287</v>
       </c>
-      <c r="E24" s="24" t="s">
+      <c r="E24" s="26" t="s">
         <v>288</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>210</v>
       </c>
-      <c r="G24" s="25" t="s">
+      <c r="G24" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H24" s="11" t="s">
@@ -6308,19 +6390,19 @@
       <c r="B25" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C25" s="23" t="s">
+      <c r="C25" s="25" t="s">
         <v>151</v>
       </c>
       <c r="D25" s="11" t="s">
         <v>290</v>
       </c>
-      <c r="E25" s="24" t="s">
+      <c r="E25" s="26" t="s">
         <v>291</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="G25" s="25" t="s">
+      <c r="G25" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H25" s="11" t="s">
@@ -6334,19 +6416,19 @@
       <c r="B26" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C26" s="23" t="s">
+      <c r="C26" s="25" t="s">
         <v>151</v>
       </c>
       <c r="D26" s="11" t="s">
         <v>293</v>
       </c>
-      <c r="E26" s="24" t="s">
+      <c r="E26" s="26" t="s">
         <v>294</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="G26" s="25" t="s">
+      <c r="G26" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H26" s="11" t="s">
@@ -6360,19 +6442,19 @@
       <c r="B27" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C27" s="23" t="s">
+      <c r="C27" s="25" t="s">
         <v>89</v>
       </c>
       <c r="D27" s="11" t="s">
         <v>296</v>
       </c>
-      <c r="E27" s="24" t="s">
+      <c r="E27" s="26" t="s">
         <v>297</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="G27" s="25" t="s">
+      <c r="G27" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H27" s="11" t="s">
@@ -6380,10 +6462,10 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E28" s="26" t="s">
+      <c r="E28" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="F28" s="27" t="n">
+      <c r="F28" s="29" t="n">
         <v>760</v>
       </c>
     </row>
@@ -6470,29 +6552,29 @@
       <c r="G4" s="21"/>
       <c r="H4" s="21"/>
     </row>
-    <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
+    <row r="6" s="23" customFormat="true" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="22" t="s">
         <v>68</v>
       </c>
     </row>
@@ -6500,22 +6582,22 @@
       <c r="A7" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C7" s="23" t="s">
+      <c r="B7" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="25" t="s">
         <v>99</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>301</v>
       </c>
-      <c r="E7" s="24" t="s">
+      <c r="E7" s="26" t="s">
         <v>302</v>
       </c>
       <c r="F7" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G7" s="25" t="s">
+      <c r="G7" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H7" s="11"/>
@@ -6524,22 +6606,22 @@
       <c r="A8" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" s="23" t="s">
+      <c r="B8" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="25" t="s">
         <v>99</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>301</v>
       </c>
-      <c r="E8" s="24" t="s">
+      <c r="E8" s="26" t="s">
         <v>303</v>
       </c>
       <c r="F8" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G8" s="25" t="s">
+      <c r="G8" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H8" s="11"/>
@@ -6548,22 +6630,22 @@
       <c r="A9" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C9" s="23" t="s">
+      <c r="B9" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" s="25" t="s">
         <v>104</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>304</v>
       </c>
-      <c r="E9" s="24" t="s">
+      <c r="E9" s="26" t="s">
         <v>305</v>
       </c>
       <c r="F9" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G9" s="25" t="s">
+      <c r="G9" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H9" s="11"/>
@@ -6572,22 +6654,22 @@
       <c r="A10" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C10" s="23" t="s">
+      <c r="B10" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C10" s="25" t="s">
         <v>104</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>304</v>
       </c>
-      <c r="E10" s="24" t="s">
+      <c r="E10" s="26" t="s">
         <v>306</v>
       </c>
       <c r="F10" s="12" t="n">
         <v>90</v>
       </c>
-      <c r="G10" s="25" t="s">
+      <c r="G10" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H10" s="11"/>
@@ -6596,22 +6678,22 @@
       <c r="A11" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C11" s="23" t="s">
+      <c r="B11" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" s="25" t="s">
         <v>104</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>304</v>
       </c>
-      <c r="E11" s="24" t="s">
+      <c r="E11" s="26" t="s">
         <v>307</v>
       </c>
       <c r="F11" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="G11" s="25" t="s">
+      <c r="G11" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H11" s="11"/>
@@ -6620,22 +6702,22 @@
       <c r="A12" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C12" s="23" t="s">
+      <c r="B12" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" s="25" t="s">
         <v>104</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>308</v>
       </c>
-      <c r="E12" s="24" t="s">
+      <c r="E12" s="26" t="s">
         <v>309</v>
       </c>
       <c r="F12" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="G12" s="25" t="s">
+      <c r="G12" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H12" s="11"/>
@@ -6644,22 +6726,22 @@
       <c r="A13" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C13" s="23" t="s">
+      <c r="B13" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13" s="25" t="s">
         <v>104</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>308</v>
       </c>
-      <c r="E13" s="24" t="s">
+      <c r="E13" s="26" t="s">
         <v>310</v>
       </c>
       <c r="F13" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G13" s="25" t="s">
+      <c r="G13" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H13" s="11" t="s">
@@ -6670,22 +6752,22 @@
       <c r="A14" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C14" s="23" t="s">
+      <c r="B14" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" s="25" t="s">
         <v>104</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>308</v>
       </c>
-      <c r="E14" s="24" t="s">
+      <c r="E14" s="26" t="s">
         <v>312</v>
       </c>
       <c r="F14" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G14" s="25" t="s">
+      <c r="G14" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H14" s="11" t="s">
@@ -6696,22 +6778,22 @@
       <c r="A15" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C15" s="23" t="s">
+      <c r="B15" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" s="25" t="s">
         <v>104</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>308</v>
       </c>
-      <c r="E15" s="24" t="s">
+      <c r="E15" s="26" t="s">
         <v>314</v>
       </c>
       <c r="F15" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G15" s="25" t="s">
+      <c r="G15" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H15" s="11"/>
@@ -6720,22 +6802,22 @@
       <c r="A16" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C16" s="23" t="s">
+      <c r="B16" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" s="25" t="s">
         <v>108</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>315</v>
       </c>
-      <c r="E16" s="24" t="s">
+      <c r="E16" s="26" t="s">
         <v>316</v>
       </c>
       <c r="F16" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="G16" s="25" t="s">
+      <c r="G16" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H16" s="11"/>
@@ -6744,22 +6826,22 @@
       <c r="A17" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="B17" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C17" s="23" t="s">
+      <c r="B17" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C17" s="25" t="s">
         <v>108</v>
       </c>
       <c r="D17" s="11" t="s">
         <v>317</v>
       </c>
-      <c r="E17" s="24" t="s">
+      <c r="E17" s="26" t="s">
         <v>318</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G17" s="25" t="s">
+      <c r="G17" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H17" s="11"/>
@@ -6768,22 +6850,22 @@
       <c r="A18" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="B18" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C18" s="23" t="s">
+      <c r="B18" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" s="25" t="s">
         <v>108</v>
       </c>
       <c r="D18" s="11" t="s">
         <v>319</v>
       </c>
-      <c r="E18" s="24" t="s">
+      <c r="E18" s="26" t="s">
         <v>320</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="G18" s="25" t="s">
+      <c r="G18" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H18" s="11"/>
@@ -6792,22 +6874,22 @@
       <c r="A19" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="B19" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C19" s="23" t="s">
+      <c r="B19" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C19" s="25" t="s">
         <v>179</v>
       </c>
       <c r="D19" s="11" t="s">
         <v>321</v>
       </c>
-      <c r="E19" s="24" t="s">
+      <c r="E19" s="26" t="s">
         <v>322</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>90</v>
       </c>
-      <c r="G19" s="25" t="s">
+      <c r="G19" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H19" s="11"/>
@@ -6819,19 +6901,19 @@
       <c r="B20" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C20" s="23" t="s">
+      <c r="C20" s="25" t="s">
         <v>99</v>
       </c>
       <c r="D20" s="11" t="s">
         <v>323</v>
       </c>
-      <c r="E20" s="24" t="s">
+      <c r="E20" s="26" t="s">
         <v>324</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>90</v>
       </c>
-      <c r="G20" s="25" t="s">
+      <c r="G20" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H20" s="11" t="s">
@@ -6845,19 +6927,19 @@
       <c r="B21" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C21" s="23" t="s">
+      <c r="C21" s="25" t="s">
         <v>104</v>
       </c>
       <c r="D21" s="11" t="s">
         <v>326</v>
       </c>
-      <c r="E21" s="24" t="s">
+      <c r="E21" s="26" t="s">
         <v>327</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="G21" s="25" t="s">
+      <c r="G21" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H21" s="11" t="s">
@@ -6871,19 +6953,19 @@
       <c r="B22" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C22" s="23" t="s">
+      <c r="C22" s="25" t="s">
         <v>104</v>
       </c>
       <c r="D22" s="11" t="s">
         <v>326</v>
       </c>
-      <c r="E22" s="24" t="s">
+      <c r="E22" s="26" t="s">
         <v>329</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="G22" s="25" t="s">
+      <c r="G22" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H22" s="11" t="s">
@@ -6897,19 +6979,19 @@
       <c r="B23" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C23" s="23" t="s">
+      <c r="C23" s="25" t="s">
         <v>108</v>
       </c>
       <c r="D23" s="11" t="s">
         <v>331</v>
       </c>
-      <c r="E23" s="24" t="s">
+      <c r="E23" s="26" t="s">
         <v>332</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G23" s="25" t="s">
+      <c r="G23" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H23" s="11" t="s">
@@ -6923,19 +7005,19 @@
       <c r="B24" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C24" s="23" t="s">
+      <c r="C24" s="25" t="s">
         <v>148</v>
       </c>
       <c r="D24" s="11" t="s">
         <v>334</v>
       </c>
-      <c r="E24" s="24" t="s">
+      <c r="E24" s="26" t="s">
         <v>335</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="G24" s="25" t="s">
+      <c r="G24" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H24" s="11" t="s">
@@ -6949,28 +7031,28 @@
       <c r="B25" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C25" s="23" t="s">
+      <c r="C25" s="25" t="s">
         <v>337</v>
       </c>
       <c r="D25" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="E25" s="24" t="s">
+      <c r="E25" s="26" t="s">
         <v>339</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="G25" s="25" t="s">
+      <c r="G25" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H25" s="11"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E26" s="26" t="s">
+      <c r="E26" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="F26" s="27" t="n">
+      <c r="F26" s="29" t="n">
         <f aca="false">SUM(F7:F25)</f>
         <v>840</v>
       </c>
@@ -7058,29 +7140,29 @@
       <c r="G4" s="21"/>
       <c r="H4" s="21"/>
     </row>
-    <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
+    <row r="6" s="23" customFormat="true" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="22" t="s">
         <v>68</v>
       </c>
     </row>
@@ -7088,22 +7170,22 @@
       <c r="A7" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C7" s="23" t="s">
+      <c r="B7" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="25" t="s">
         <v>99</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>342</v>
       </c>
-      <c r="E7" s="24" t="s">
+      <c r="E7" s="26" t="s">
         <v>343</v>
       </c>
       <c r="F7" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G7" s="25" t="s">
+      <c r="G7" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H7" s="11"/>
@@ -7112,22 +7194,22 @@
       <c r="A8" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" s="23" t="s">
+      <c r="B8" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="25" t="s">
         <v>104</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>344</v>
       </c>
-      <c r="E8" s="24" t="s">
+      <c r="E8" s="26" t="s">
         <v>345</v>
       </c>
       <c r="F8" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G8" s="25" t="s">
+      <c r="G8" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H8" s="11"/>
@@ -7136,22 +7218,22 @@
       <c r="A9" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C9" s="23" t="s">
+      <c r="B9" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" s="25" t="s">
         <v>104</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>344</v>
       </c>
-      <c r="E9" s="24" t="s">
+      <c r="E9" s="26" t="s">
         <v>346</v>
       </c>
       <c r="F9" s="12" t="n">
         <v>120</v>
       </c>
-      <c r="G9" s="25" t="s">
+      <c r="G9" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H9" s="11"/>
@@ -7160,22 +7242,22 @@
       <c r="A10" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C10" s="23" t="s">
+      <c r="B10" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C10" s="25" t="s">
         <v>104</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>344</v>
       </c>
-      <c r="E10" s="24" t="s">
+      <c r="E10" s="26" t="s">
         <v>347</v>
       </c>
       <c r="F10" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="G10" s="25" t="s">
+      <c r="G10" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H10" s="11"/>
@@ -7184,22 +7266,22 @@
       <c r="A11" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C11" s="23" t="s">
+      <c r="B11" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" s="25" t="s">
         <v>104</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>344</v>
       </c>
-      <c r="E11" s="24" t="s">
+      <c r="E11" s="26" t="s">
         <v>348</v>
       </c>
       <c r="F11" s="12" t="n">
         <v>90</v>
       </c>
-      <c r="G11" s="25" t="s">
+      <c r="G11" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H11" s="11"/>
@@ -7208,22 +7290,22 @@
       <c r="A12" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C12" s="23" t="s">
+      <c r="B12" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" s="25" t="s">
         <v>104</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>344</v>
       </c>
-      <c r="E12" s="24" t="s">
+      <c r="E12" s="26" t="s">
         <v>349</v>
       </c>
       <c r="F12" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="G12" s="25" t="s">
+      <c r="G12" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H12" s="11"/>
@@ -7232,22 +7314,22 @@
       <c r="A13" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C13" s="23" t="s">
+      <c r="B13" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13" s="25" t="s">
         <v>151</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="E13" s="24" t="s">
+      <c r="E13" s="26" t="s">
         <v>351</v>
       </c>
       <c r="F13" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="G13" s="25" t="s">
+      <c r="G13" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H13" s="11"/>
@@ -7256,22 +7338,22 @@
       <c r="A14" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C14" s="23" t="s">
+      <c r="B14" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" s="25" t="s">
         <v>89</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>352</v>
       </c>
-      <c r="E14" s="24" t="s">
+      <c r="E14" s="26" t="s">
         <v>353</v>
       </c>
       <c r="F14" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="G14" s="25" t="s">
+      <c r="G14" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H14" s="11" t="s">
@@ -7282,22 +7364,22 @@
       <c r="A15" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C15" s="23" t="s">
+      <c r="B15" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" s="25" t="s">
         <v>99</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>355</v>
       </c>
-      <c r="E15" s="24" t="s">
+      <c r="E15" s="26" t="s">
         <v>356</v>
       </c>
       <c r="F15" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G15" s="25" t="s">
+      <c r="G15" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H15" s="11"/>
@@ -7306,22 +7388,22 @@
       <c r="A16" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C16" s="23" t="s">
+      <c r="B16" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" s="25" t="s">
         <v>99</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>355</v>
       </c>
-      <c r="E16" s="24" t="s">
+      <c r="E16" s="26" t="s">
         <v>357</v>
       </c>
       <c r="F16" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G16" s="25" t="s">
+      <c r="G16" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H16" s="11"/>
@@ -7330,22 +7412,22 @@
       <c r="A17" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="B17" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C17" s="23" t="s">
+      <c r="B17" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C17" s="25" t="s">
         <v>99</v>
       </c>
       <c r="D17" s="11" t="s">
         <v>355</v>
       </c>
-      <c r="E17" s="24" t="s">
+      <c r="E17" s="26" t="s">
         <v>358</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G17" s="25" t="s">
+      <c r="G17" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H17" s="11"/>
@@ -7354,22 +7436,22 @@
       <c r="A18" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="B18" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C18" s="23" t="s">
+      <c r="B18" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" s="25" t="s">
         <v>104</v>
       </c>
       <c r="D18" s="11" t="s">
         <v>359</v>
       </c>
-      <c r="E18" s="24" t="s">
+      <c r="E18" s="26" t="s">
         <v>360</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>120</v>
       </c>
-      <c r="G18" s="25" t="s">
+      <c r="G18" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H18" s="11"/>
@@ -7378,22 +7460,22 @@
       <c r="A19" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="B19" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C19" s="23" t="s">
+      <c r="B19" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C19" s="25" t="s">
         <v>108</v>
       </c>
       <c r="D19" s="11" t="s">
         <v>361</v>
       </c>
-      <c r="E19" s="24" t="s">
+      <c r="E19" s="26" t="s">
         <v>362</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G19" s="25" t="s">
+      <c r="G19" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H19" s="11"/>
@@ -7402,22 +7484,22 @@
       <c r="A20" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="B20" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C20" s="23" t="s">
+      <c r="B20" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C20" s="25" t="s">
         <v>179</v>
       </c>
       <c r="D20" s="11" t="s">
         <v>363</v>
       </c>
-      <c r="E20" s="24" t="s">
+      <c r="E20" s="26" t="s">
         <v>364</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="G20" s="25" t="s">
+      <c r="G20" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H20" s="11"/>
@@ -7429,19 +7511,19 @@
       <c r="B21" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C21" s="23" t="s">
+      <c r="C21" s="25" t="s">
         <v>99</v>
       </c>
       <c r="D21" s="11" t="s">
         <v>365</v>
       </c>
-      <c r="E21" s="24" t="s">
+      <c r="E21" s="26" t="s">
         <v>366</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>90</v>
       </c>
-      <c r="G21" s="25" t="s">
+      <c r="G21" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H21" s="11"/>
@@ -7453,19 +7535,19 @@
       <c r="B22" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C22" s="23" t="s">
+      <c r="C22" s="25" t="s">
         <v>104</v>
       </c>
       <c r="D22" s="11" t="s">
         <v>367</v>
       </c>
-      <c r="E22" s="24" t="s">
+      <c r="E22" s="26" t="s">
         <v>368</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>120</v>
       </c>
-      <c r="G22" s="25" t="s">
+      <c r="G22" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H22" s="11"/>
@@ -7477,19 +7559,19 @@
       <c r="B23" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C23" s="23" t="s">
+      <c r="C23" s="25" t="s">
         <v>108</v>
       </c>
       <c r="D23" s="11" t="s">
         <v>369</v>
       </c>
-      <c r="E23" s="24" t="s">
+      <c r="E23" s="26" t="s">
         <v>370</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="G23" s="25" t="s">
+      <c r="G23" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H23" s="11"/>
@@ -7501,28 +7583,28 @@
       <c r="B24" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C24" s="23" t="s">
+      <c r="C24" s="25" t="s">
         <v>179</v>
       </c>
       <c r="D24" s="11" t="s">
         <v>371</v>
       </c>
-      <c r="E24" s="24" t="s">
+      <c r="E24" s="26" t="s">
         <v>372</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="G24" s="25" t="s">
+      <c r="G24" s="27" t="s">
         <v>3</v>
       </c>
       <c r="H24" s="11"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E25" s="26" t="s">
+      <c r="E25" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="F25" s="27" t="n">
+      <c r="F25" s="29" t="n">
         <f aca="false">SUM(F7:F24)</f>
         <v>1020</v>
       </c>
